--- a/data/mini-example-resilience/Power_BusInfo.xlsx
+++ b/data/mini-example-resilience/Power_BusInfo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\Mini-example-resilience\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\mini-example-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C02C97-93FF-406F-9EB9-A77FECECD5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BCDF0B-D9BF-4A3C-AE72-3CA8F48F8811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="67">
   <si>
     <t>Power - Bus information</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>StylizedSystem</t>
+  </si>
+  <si>
+    <t>Node_feedin</t>
   </si>
 </sst>
 </file>
@@ -1114,19 +1117,45 @@
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="B9" s="11"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="18"/>
+      <c r="C9" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="13">
+        <v>220</v>
+      </c>
+      <c r="F9" s="14">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0.9</v>
+      </c>
+      <c r="H9" s="14">
+        <v>0</v>
+      </c>
+      <c r="I9" s="14">
+        <v>0</v>
+      </c>
+      <c r="J9" s="15">
+        <v>0.95</v>
+      </c>
+      <c r="K9" s="16">
+        <v>2000</v>
+      </c>
+      <c r="L9" s="16">
+        <v>2023</v>
+      </c>
+      <c r="M9" s="17">
+        <v>47.272599999999997</v>
+      </c>
+      <c r="N9" s="17">
+        <v>11.471399999999999</v>
+      </c>
+      <c r="O9" s="18">
+        <v>1</v>
+      </c>
       <c r="P9" s="19"/>
       <c r="Q9" s="19"/>
     </row>
